--- a/从零开始学Slots/从零开始学Slots-43-数值篇-Grid.xlsx
+++ b/从零开始学Slots/从零开始学Slots-43-数值篇-Grid.xlsx
@@ -7637,6 +7637,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N175" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -9425,5 +9428,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M138" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-43-数值篇-Grid.xlsx
+++ b/从零开始学Slots/从零开始学Slots-43-数值篇-Grid.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="205">
   <si>
     <r>
       <rPr>
@@ -6483,7 +6483,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6634,6 +6634,14 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -7129,13 +7137,13 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="s">
-        <v>41</v>
+      <c r="A54" s="38">
+        <v>9</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
-        <v>42</v>
+      <c r="A55" s="38">
+        <v>2</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9269,8 +9277,8 @@
       <c r="F108" s="13"/>
     </row>
     <row r="109" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="17" t="s">
-        <v>189</v>
+      <c r="A109" s="39">
+        <v>10</v>
       </c>
       <c r="B109" s="32" t="n">
         <v>0.540658</v>

--- a/从零开始学Slots/从零开始学Slots-43-数值篇-Grid.xlsx
+++ b/从零开始学Slots/从零开始学Slots-43-数值篇-Grid.xlsx
@@ -6293,13 +6293,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.0000%"/>
     <numFmt numFmtId="169" formatCode="0.000000%"/>
+    <numFmt numFmtId="170" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -6483,7 +6484,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6641,6 +6642,30 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7996,7 +8021,7 @@
       <c r="A26" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="B26" s="23" t="n">
+      <c r="B26" s="41" t="n">
         <f aca="false">SUM(B15:B25)</f>
         <v>1</v>
       </c>
@@ -8093,7 +8118,7 @@
       <c r="A34" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="B34" s="23" t="n">
+      <c r="B34" s="41" t="n">
         <f aca="false">SUM(B30:B33)</f>
         <v>1</v>
       </c>
@@ -8251,7 +8276,7 @@
       <c r="B46" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="C46" s="25" t="n">
+      <c r="C46" s="42" t="n">
         <f aca="false">(BINOMDIST(9,$B$7,$B$15,TRUE())-BINOMDIST(7,$B$7,$B$15,TRUE()))*B38+(BINOMDIST(11,$B$7,$B$15,TRUE())-BINOMDIST(9,$B$7,$B$15,TRUE()))*C38+(1-BINOMDIST(11,$B$7,$B$15,TRUE()))*D38</f>
         <v>0.17934498534376</v>
       </c>
@@ -8293,7 +8318,7 @@
       <c r="A50" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="B50" s="26" t="n">
+      <c r="B50" s="43" t="n">
         <f aca="false">BINOMDIST($A50,$B$7,$B$25,FALSE())</f>
         <v>0.354253208571123</v>
       </c>
@@ -8301,11 +8326,11 @@
         <f aca="false">$B$7-$A50</f>
         <v>30</v>
       </c>
-      <c r="D50" s="28" t="n">
+      <c r="D50" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C50),C50,$B$15,TRUE())-BINOMDIST(MIN(7,C50),C50,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C50),C50,$B$15,TRUE())-BINOMDIST(MIN(9,C50),C50,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C50),C50,$B$15,TRUE()))*$D$38)</f>
         <v>0.564936703832844</v>
       </c>
-      <c r="E50" s="26" t="n">
+      <c r="E50" s="43" t="n">
         <f aca="false">B50*D50</f>
         <v>0.20013063997238</v>
       </c>
@@ -8314,7 +8339,7 @@
       <c r="A51" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B51" s="26" t="n">
+      <c r="B51" s="43" t="n">
         <f aca="false">BINOMDIST($A51,$B$7,$B$25,FALSE())</f>
         <v>0.374056182963298</v>
       </c>
@@ -8322,11 +8347,11 @@
         <f aca="false">$B$7-$A51</f>
         <v>29</v>
       </c>
-      <c r="D51" s="28" t="n">
+      <c r="D51" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C51),C51,$B$15,TRUE())-BINOMDIST(MIN(7,C51),C51,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C51),C51,$B$15,TRUE())-BINOMDIST(MIN(9,C51),C51,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C51),C51,$B$15,TRUE()))*$D$38)</f>
         <v>0.446860910624285</v>
       </c>
-      <c r="E51" s="26" t="n">
+      <c r="E51" s="43" t="n">
         <f aca="false">B51*D51</f>
         <v>0.167151086543624</v>
       </c>
@@ -8335,7 +8360,7 @@
       <c r="A52" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B52" s="26" t="n">
+      <c r="B52" s="43" t="n">
         <f aca="false">BINOMDIST($A52,$B$7,$B$25,FALSE())</f>
         <v>0.19090030869659</v>
       </c>
@@ -8343,11 +8368,11 @@
         <f aca="false">$B$7-$A52</f>
         <v>28</v>
       </c>
-      <c r="D52" s="28" t="n">
+      <c r="D52" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C52),C52,$B$15,TRUE())-BINOMDIST(MIN(7,C52),C52,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C52),C52,$B$15,TRUE())-BINOMDIST(MIN(9,C52),C52,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C52),C52,$B$15,TRUE()))*$D$38)</f>
         <v>0.349394915619037</v>
       </c>
-      <c r="E52" s="26" t="n">
+      <c r="E52" s="43" t="n">
         <f aca="false">B52*D52</f>
         <v>0.0666995972486932</v>
       </c>
@@ -8356,7 +8381,7 @@
       <c r="A53" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B53" s="26" t="n">
+      <c r="B53" s="43" t="n">
         <f aca="false">BINOMDIST($A53,$B$7,$B$25,FALSE())</f>
         <v>0.0627112125186866</v>
       </c>
@@ -8364,11 +8389,11 @@
         <f aca="false">$B$7-$A53</f>
         <v>27</v>
       </c>
-      <c r="D53" s="28" t="n">
+      <c r="D53" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C53),C53,$B$15,TRUE())-BINOMDIST(MIN(7,C53),C53,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C53),C53,$B$15,TRUE())-BINOMDIST(MIN(9,C53),C53,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C53),C53,$B$15,TRUE()))*$D$38)</f>
         <v>0.269751915257086</v>
       </c>
-      <c r="E53" s="26" t="n">
+      <c r="E53" s="43" t="n">
         <f aca="false">B53*D53</f>
         <v>0.0169164696850098</v>
       </c>
@@ -8377,7 +8402,7 @@
       <c r="A54" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B54" s="26" t="n">
+      <c r="B54" s="43" t="n">
         <f aca="false">BINOMDIST($A54,$B$7,$B$25,FALSE())</f>
         <v>0.0148987818561476</v>
       </c>
@@ -8385,11 +8410,11 @@
         <f aca="false">$B$7-$A54</f>
         <v>26</v>
       </c>
-      <c r="D54" s="28" t="n">
+      <c r="D54" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C54),C54,$B$15,TRUE())-BINOMDIST(MIN(7,C54),C54,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C54),C54,$B$15,TRUE())-BINOMDIST(MIN(9,C54),C54,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C54),C54,$B$15,TRUE()))*$D$38)</f>
         <v>0.205392186293125</v>
       </c>
-      <c r="E54" s="26" t="n">
+      <c r="E54" s="43" t="n">
         <f aca="false">B54*D54</f>
         <v>0.00306009337853849</v>
       </c>
@@ -8398,7 +8423,7 @@
       <c r="A55" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B55" s="26" t="n">
+      <c r="B55" s="43" t="n">
         <f aca="false">BINOMDIST($A55,$B$7,$B$25,FALSE())</f>
         <v>0.00272681638940672</v>
       </c>
@@ -8406,11 +8431,11 @@
         <f aca="false">$B$7-$A55</f>
         <v>25</v>
       </c>
-      <c r="D55" s="28" t="n">
+      <c r="D55" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C55),C55,$B$15,TRUE())-BINOMDIST(MIN(7,C55),C55,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C55),C55,$B$15,TRUE())-BINOMDIST(MIN(9,C55),C55,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C55),C55,$B$15,TRUE()))*$D$38)</f>
         <v>0.154016020491661</v>
       </c>
-      <c r="E55" s="26" t="n">
+      <c r="E55" s="43" t="n">
         <f aca="false">B55*D55</f>
         <v>0.000419973408907864</v>
       </c>
@@ -8419,7 +8444,7 @@
       <c r="A56" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B56" s="26" t="n">
+      <c r="B56" s="43" t="n">
         <f aca="false">BINOMDIST($A56,$B$7,$B$25,FALSE())</f>
         <v>0.000399895433229074</v>
       </c>
@@ -8427,11 +8452,11 @@
         <f aca="false">$B$7-$A56</f>
         <v>24</v>
       </c>
-      <c r="D56" s="28" t="n">
+      <c r="D56" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C56),C56,$B$15,TRUE())-BINOMDIST(MIN(7,C56),C56,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C56),C56,$B$15,TRUE())-BINOMDIST(MIN(9,C56),C56,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C56),C56,$B$15,TRUE()))*$D$38)</f>
         <v>0.113555970223684</v>
       </c>
-      <c r="E56" s="26" t="n">
+      <c r="E56" s="43" t="n">
         <f aca="false">B56*D56</f>
         <v>4.54105139083481E-005</v>
       </c>
@@ -8440,7 +8465,7 @@
       <c r="A57" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B57" s="26" t="n">
+      <c r="B57" s="43" t="n">
         <f aca="false">BINOMDIST($A57,$B$7,$B$25,FALSE())</f>
         <v>4.8257124151867E-005</v>
       </c>
@@ -8448,11 +8473,11 @@
         <f aca="false">$B$7-$A57</f>
         <v>23</v>
       </c>
-      <c r="D57" s="28" t="n">
+      <c r="D57" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C57),C57,$B$15,TRUE())-BINOMDIST(MIN(7,C57),C57,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C57),C57,$B$15,TRUE())-BINOMDIST(MIN(9,C57),C57,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C57),C57,$B$15,TRUE()))*$D$38)</f>
         <v>0.082168376084359</v>
       </c>
-      <c r="E57" s="26" t="n">
+      <c r="E57" s="43" t="n">
         <f aca="false">B57*D57</f>
         <v>3.96520952606021E-006</v>
       </c>
@@ -8461,7 +8486,7 @@
       <c r="A58" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B58" s="26" t="n">
+      <c r="B58" s="43" t="n">
         <f aca="false">BINOMDIST($A58,$B$7,$B$25,FALSE())</f>
         <v>4.88316137251035E-006</v>
       </c>
@@ -8469,11 +8494,11 @@
         <f aca="false">$B$7-$A58</f>
         <v>22</v>
       </c>
-      <c r="D58" s="28" t="n">
+      <c r="D58" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C58),C58,$B$15,TRUE())-BINOMDIST(MIN(7,C58),C58,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C58),C58,$B$15,TRUE())-BINOMDIST(MIN(9,C58),C58,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C58),C58,$B$15,TRUE()))*$D$38)</f>
         <v>0.0582241252034346</v>
       </c>
-      <c r="E58" s="26" t="n">
+      <c r="E58" s="43" t="n">
         <f aca="false">B58*D58</f>
         <v>2.84317799141618E-007</v>
       </c>
@@ -8482,7 +8507,7 @@
       <c r="A59" s="14" t="n">
         <v>9</v>
       </c>
-      <c r="B59" s="26" t="n">
+      <c r="B59" s="43" t="n">
         <f aca="false">BINOMDIST($A59,$B$7,$B$25,FALSE())</f>
         <v>4.20129365842851E-007</v>
       </c>
@@ -8490,11 +8515,11 @@
         <f aca="false">$B$7-$A59</f>
         <v>21</v>
       </c>
-      <c r="D59" s="28" t="n">
+      <c r="D59" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C59),C59,$B$15,TRUE())-BINOMDIST(MIN(7,C59),C59,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C59),C59,$B$15,TRUE())-BINOMDIST(MIN(9,C59),C59,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C59),C59,$B$15,TRUE()))*$D$38)</f>
         <v>0.0402985759393029</v>
       </c>
-      <c r="E59" s="26" t="n">
+      <c r="E59" s="43" t="n">
         <f aca="false">B59*D59</f>
         <v>1.69306151537493E-008</v>
       </c>
@@ -8503,7 +8528,7 @@
       <c r="A60" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="B60" s="26" t="n">
+      <c r="B60" s="43" t="n">
         <f aca="false">BINOMDIST($A60,$B$7,$B$25,FALSE())</f>
         <v>3.10530400840368E-008</v>
       </c>
@@ -8511,11 +8536,11 @@
         <f aca="false">$B$7-$A60</f>
         <v>20</v>
       </c>
-      <c r="D60" s="28" t="n">
+      <c r="D60" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C60),C60,$B$15,TRUE())-BINOMDIST(MIN(7,C60),C60,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C60),C60,$B$15,TRUE())-BINOMDIST(MIN(9,C60),C60,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C60),C60,$B$15,TRUE()))*$D$38)</f>
         <v>0.027160583451702</v>
       </c>
-      <c r="E60" s="26" t="n">
+      <c r="E60" s="43" t="n">
         <f aca="false">B60*D60</f>
         <v>8.43418686631529E-010</v>
       </c>
@@ -8524,7 +8549,7 @@
       <c r="A61" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B61" s="26" t="n">
+      <c r="B61" s="43" t="n">
         <f aca="false">BINOMDIST($A61,$B$7,$B$25,FALSE())</f>
         <v>1.98720753408103E-009</v>
       </c>
@@ -8532,11 +8557,11 @@
         <f aca="false">$B$7-$A61</f>
         <v>19</v>
       </c>
-      <c r="D61" s="28" t="n">
+      <c r="D61" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C61),C61,$B$15,TRUE())-BINOMDIST(MIN(7,C61),C61,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C61),C61,$B$15,TRUE())-BINOMDIST(MIN(9,C61),C61,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C61),C61,$B$15,TRUE()))*$D$38)</f>
         <v>0.017760573023312</v>
       </c>
-      <c r="E61" s="26" t="n">
+      <c r="E61" s="43" t="n">
         <f aca="false">B61*D61</f>
         <v>3.52939445215219E-011</v>
       </c>
@@ -8545,7 +8570,7 @@
       <c r="A62" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="B62" s="26" t="n">
+      <c r="B62" s="43" t="n">
         <f aca="false">BINOMDIST($A62,$B$7,$B$25,FALSE())</f>
         <v>1.1074327700279E-010</v>
       </c>
@@ -8553,11 +8578,11 @@
         <f aca="false">$B$7-$A62</f>
         <v>18</v>
       </c>
-      <c r="D62" s="28" t="n">
+      <c r="D62" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C62),C62,$B$15,TRUE())-BINOMDIST(MIN(7,C62),C62,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C62),C62,$B$15,TRUE())-BINOMDIST(MIN(9,C62),C62,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C62),C62,$B$15,TRUE()))*$D$38)</f>
         <v>0.0112176351206867</v>
       </c>
-      <c r="E62" s="26" t="n">
+      <c r="E62" s="43" t="n">
         <f aca="false">B62*D62</f>
         <v>1.24227767348643E-012</v>
       </c>
@@ -8566,7 +8591,7 @@
       <c r="A63" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="B63" s="26" t="n">
+      <c r="B63" s="43" t="n">
         <f aca="false">BINOMDIST($A63,$B$7,$B$25,FALSE())</f>
         <v>5.39694899870263E-012</v>
       </c>
@@ -8574,11 +8599,11 @@
         <f aca="false">$B$7-$A63</f>
         <v>17</v>
       </c>
-      <c r="D63" s="28" t="n">
+      <c r="D63" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C63),C63,$B$15,TRUE())-BINOMDIST(MIN(7,C63),C63,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C63),C63,$B$15,TRUE())-BINOMDIST(MIN(9,C63),C63,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C63),C63,$B$15,TRUE()))*$D$38)</f>
         <v>0.00680565833881258</v>
       </c>
-      <c r="E63" s="26" t="n">
+      <c r="E63" s="43" t="n">
         <f aca="false">B63*D63</f>
         <v>3.67297909571668E-014</v>
       </c>
@@ -8587,7 +8612,7 @@
       <c r="A64" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="B64" s="26" t="n">
+      <c r="B64" s="43" t="n">
         <f aca="false">BINOMDIST($A64,$B$7,$B$25,FALSE())</f>
         <v>2.30659310947214E-013</v>
       </c>
@@ -8595,11 +8620,11 @@
         <f aca="false">$B$7-$A64</f>
         <v>16</v>
       </c>
-      <c r="D64" s="28" t="n">
+      <c r="D64" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C64),C64,$B$15,TRUE())-BINOMDIST(MIN(7,C64),C64,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C64),C64,$B$15,TRUE())-BINOMDIST(MIN(9,C64),C64,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C64),C64,$B$15,TRUE()))*$D$38)</f>
         <v>0.0039385727132383</v>
       </c>
-      <c r="E64" s="26" t="n">
+      <c r="E64" s="43" t="n">
         <f aca="false">B64*D64</f>
         <v>9.08468468151046E-016</v>
       </c>
@@ -8608,7 +8633,7 @@
       <c r="A65" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="B65" s="26" t="n">
+      <c r="B65" s="43" t="n">
         <f aca="false">BINOMDIST($A65,$B$7,$B$25,FALSE())</f>
         <v>8.65967323362901E-015</v>
       </c>
@@ -8616,11 +8641,11 @@
         <f aca="false">$B$7-$A65</f>
         <v>15</v>
       </c>
-      <c r="D65" s="28" t="n">
+      <c r="D65" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C65),C65,$B$15,TRUE())-BINOMDIST(MIN(7,C65),C65,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C65),C65,$B$15,TRUE())-BINOMDIST(MIN(9,C65),C65,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C65),C65,$B$15,TRUE()))*$D$38)</f>
         <v>0.00215484423820966</v>
       </c>
-      <c r="E65" s="26" t="n">
+      <c r="E65" s="43" t="n">
         <f aca="false">B65*D65</f>
         <v>1.86602469722639E-017</v>
       </c>
@@ -8629,7 +8654,7 @@
       <c r="A66" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B66" s="26" t="n">
+      <c r="B66" s="43" t="n">
         <f aca="false">BINOMDIST($A66,$B$7,$B$25,FALSE())</f>
         <v>2.85742323314622E-016</v>
       </c>
@@ -8637,11 +8662,11 @@
         <f aca="false">$B$7-$A66</f>
         <v>14</v>
       </c>
-      <c r="D66" s="28" t="n">
+      <c r="D66" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C66),C66,$B$15,TRUE())-BINOMDIST(MIN(7,C66),C66,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C66),C66,$B$15,TRUE())-BINOMDIST(MIN(9,C66),C66,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C66),C66,$B$15,TRUE()))*$D$38)</f>
         <v>0.00110143809598326</v>
       </c>
-      <c r="E66" s="26" t="n">
+      <c r="E66" s="43" t="n">
         <f aca="false">B66*D66</f>
         <v>3.1472748053349E-019</v>
       </c>
@@ -8650,7 +8675,7 @@
       <c r="A67" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="B67" s="26" t="n">
+      <c r="B67" s="43" t="n">
         <f aca="false">BINOMDIST($A67,$B$7,$B$25,FALSE())</f>
         <v>8.28238618303252E-018</v>
       </c>
@@ -8658,11 +8683,11 @@
         <f aca="false">$B$7-$A67</f>
         <v>13</v>
       </c>
-      <c r="D67" s="28" t="n">
+      <c r="D67" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C67),C67,$B$15,TRUE())-BINOMDIST(MIN(7,C67),C67,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C67),C67,$B$15,TRUE())-BINOMDIST(MIN(9,C67),C67,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C67),C67,$B$15,TRUE()))*$D$38)</f>
         <v>0.000517547567055438</v>
       </c>
-      <c r="E67" s="26" t="n">
+      <c r="E67" s="43" t="n">
         <f aca="false">B67*D67</f>
         <v>4.28652881844205E-021</v>
       </c>
@@ -8671,7 +8696,7 @@
       <c r="A68" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="B68" s="26" t="n">
+      <c r="B68" s="43" t="n">
         <f aca="false">BINOMDIST($A68,$B$7,$B$25,FALSE())</f>
         <v>2.10536846842672E-019</v>
       </c>
@@ -8679,11 +8704,11 @@
         <f aca="false">$B$7-$A68</f>
         <v>12</v>
       </c>
-      <c r="D68" s="28" t="n">
+      <c r="D68" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C68),C68,$B$15,TRUE())-BINOMDIST(MIN(7,C68),C68,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C68),C68,$B$15,TRUE())-BINOMDIST(MIN(9,C68),C68,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C68),C68,$B$15,TRUE()))*$D$38)</f>
         <v>0.000218460635092399</v>
       </c>
-      <c r="E68" s="26" t="n">
+      <c r="E68" s="43" t="n">
         <f aca="false">B68*D68</f>
         <v>4.59940132716012E-023</v>
       </c>
@@ -8692,7 +8717,7 @@
       <c r="A69" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="B69" s="26" t="n">
+      <c r="B69" s="43" t="n">
         <f aca="false">BINOMDIST($A69,$B$7,$B$25,FALSE())</f>
         <v>4.68012604946115E-021</v>
       </c>
@@ -8700,11 +8725,11 @@
         <f aca="false">$B$7-$A69</f>
         <v>11</v>
       </c>
-      <c r="D69" s="28" t="n">
+      <c r="D69" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C69),C69,$B$15,TRUE())-BINOMDIST(MIN(7,C69),C69,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C69),C69,$B$15,TRUE())-BINOMDIST(MIN(9,C69),C69,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C69),C69,$B$15,TRUE()))*$D$38)</f>
         <v>7.99977953383213E-005</v>
       </c>
-      <c r="E69" s="26" t="n">
+      <c r="E69" s="43" t="n">
         <f aca="false">B69*D69</f>
         <v>3.74399765862339E-025</v>
       </c>
@@ -8713,7 +8738,7 @@
       <c r="A70" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="B70" s="26" t="n">
+      <c r="B70" s="43" t="n">
         <f aca="false">BINOMDIST($A70,$B$7,$B$25,FALSE())</f>
         <v>9.0598713379838E-023</v>
       </c>
@@ -8721,11 +8746,11 @@
         <f aca="false">$B$7-$A70</f>
         <v>10</v>
       </c>
-      <c r="D70" s="28" t="n">
+      <c r="D70" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C70),C70,$B$15,TRUE())-BINOMDIST(MIN(7,C70),C70,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C70),C70,$B$15,TRUE())-BINOMDIST(MIN(9,C70),C70,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C70),C70,$B$15,TRUE()))*$D$38)</f>
         <v>2.39918527697169E-005</v>
       </c>
-      <c r="E70" s="26" t="n">
+      <c r="E70" s="43" t="n">
         <f aca="false">B70*D70</f>
         <v>2.17363099253486E-027</v>
       </c>
@@ -8734,7 +8759,7 @@
       <c r="A71" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="B71" s="26" t="n">
+      <c r="B71" s="43" t="n">
         <f aca="false">BINOMDIST($A71,$B$7,$B$25,FALSE())</f>
         <v>1.51846409095657E-024</v>
       </c>
@@ -8742,11 +8767,11 @@
         <f aca="false">$B$7-$A71</f>
         <v>9</v>
       </c>
-      <c r="D71" s="28" t="n">
+      <c r="D71" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C71),C71,$B$15,TRUE())-BINOMDIST(MIN(7,C71),C71,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C71),C71,$B$15,TRUE())-BINOMDIST(MIN(9,C71),C71,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C71),C71,$B$15,TRUE()))*$D$38)</f>
         <v>5.28182802170263E-006</v>
       </c>
-      <c r="E71" s="26" t="n">
+      <c r="E71" s="43" t="n">
         <f aca="false">B71*D71</f>
         <v>8.02026618556361E-030</v>
       </c>
@@ -8755,7 +8780,7 @@
       <c r="A72" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="B72" s="26" t="n">
+      <c r="B72" s="43" t="n">
         <f aca="false">BINOMDIST($A72,$B$7,$B$25,FALSE())</f>
         <v>2.18638251379969E-026</v>
       </c>
@@ -8763,11 +8788,11 @@
         <f aca="false">$B$7-$A72</f>
         <v>8</v>
       </c>
-      <c r="D72" s="28" t="n">
+      <c r="D72" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C72),C72,$B$15,TRUE())-BINOMDIST(MIN(7,C72),C72,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C72),C72,$B$15,TRUE())-BINOMDIST(MIN(9,C72),C72,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C72),C72,$B$15,TRUE()))*$D$38)</f>
         <v>6.46648874697009E-007</v>
       </c>
-      <c r="E72" s="26" t="n">
+      <c r="E72" s="43" t="n">
         <f aca="false">B72*D72</f>
         <v>1.41382179220579E-032</v>
       </c>
@@ -8776,7 +8801,7 @@
       <c r="A73" s="14" t="n">
         <v>23</v>
       </c>
-      <c r="B73" s="26" t="n">
+      <c r="B73" s="43" t="n">
         <f aca="false">BINOMDIST($A73,$B$7,$B$25,FALSE())</f>
         <v>2.67664075863496E-028</v>
       </c>
@@ -8784,11 +8809,11 @@
         <f aca="false">$B$7-$A73</f>
         <v>7</v>
       </c>
-      <c r="D73" s="28" t="n">
+      <c r="D73" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C73),C73,$B$15,TRUE())-BINOMDIST(MIN(7,C73),C73,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C73),C73,$B$15,TRUE())-BINOMDIST(MIN(9,C73),C73,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C73),C73,$B$15,TRUE()))*$D$38)</f>
         <v>0</v>
       </c>
-      <c r="E73" s="26" t="n">
+      <c r="E73" s="43" t="n">
         <f aca="false">B73*D73</f>
         <v>0</v>
       </c>
@@ -8797,7 +8822,7 @@
       <c r="A74" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="B74" s="26" t="n">
+      <c r="B74" s="43" t="n">
         <f aca="false">BINOMDIST($A74,$B$7,$B$25,FALSE())</f>
         <v>2.74775923289821E-030</v>
       </c>
@@ -8805,11 +8830,11 @@
         <f aca="false">$B$7-$A74</f>
         <v>6</v>
       </c>
-      <c r="D74" s="28" t="n">
+      <c r="D74" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C74),C74,$B$15,TRUE())-BINOMDIST(MIN(7,C74),C74,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C74),C74,$B$15,TRUE())-BINOMDIST(MIN(9,C74),C74,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C74),C74,$B$15,TRUE()))*$D$38)</f>
         <v>0</v>
       </c>
-      <c r="E74" s="26" t="n">
+      <c r="E74" s="43" t="n">
         <f aca="false">B74*D74</f>
         <v>0</v>
       </c>
@@ -8818,7 +8843,7 @@
       <c r="A75" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="B75" s="26" t="n">
+      <c r="B75" s="43" t="n">
         <f aca="false">BINOMDIST($A75,$B$7,$B$25,FALSE())</f>
         <v>2.32108854455998E-032</v>
       </c>
@@ -8826,11 +8851,11 @@
         <f aca="false">$B$7-$A75</f>
         <v>5</v>
       </c>
-      <c r="D75" s="28" t="n">
+      <c r="D75" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C75),C75,$B$15,TRUE())-BINOMDIST(MIN(7,C75),C75,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C75),C75,$B$15,TRUE())-BINOMDIST(MIN(9,C75),C75,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C75),C75,$B$15,TRUE()))*$D$38)</f>
         <v>0</v>
       </c>
-      <c r="E75" s="26" t="n">
+      <c r="E75" s="43" t="n">
         <f aca="false">B75*D75</f>
         <v>0</v>
       </c>
@@ -8839,7 +8864,7 @@
       <c r="A76" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="B76" s="26" t="n">
+      <c r="B76" s="43" t="n">
         <f aca="false">BINOMDIST($A76,$B$7,$B$25,FALSE())</f>
         <v>1.5710505358146E-034</v>
       </c>
@@ -8847,11 +8872,11 @@
         <f aca="false">$B$7-$A76</f>
         <v>4</v>
       </c>
-      <c r="D76" s="28" t="n">
+      <c r="D76" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C76),C76,$B$15,TRUE())-BINOMDIST(MIN(7,C76),C76,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C76),C76,$B$15,TRUE())-BINOMDIST(MIN(9,C76),C76,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C76),C76,$B$15,TRUE()))*$D$38)</f>
         <v>0</v>
       </c>
-      <c r="E76" s="26" t="n">
+      <c r="E76" s="43" t="n">
         <f aca="false">B76*D76</f>
         <v>0</v>
       </c>
@@ -8860,7 +8885,7 @@
       <c r="A77" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="B77" s="26" t="n">
+      <c r="B77" s="43" t="n">
         <f aca="false">BINOMDIST($A77,$B$7,$B$25,FALSE())</f>
         <v>8.19196660036754E-037</v>
       </c>
@@ -8868,11 +8893,11 @@
         <f aca="false">$B$7-$A77</f>
         <v>3</v>
       </c>
-      <c r="D77" s="28" t="n">
+      <c r="D77" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C77),C77,$B$15,TRUE())-BINOMDIST(MIN(7,C77),C77,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C77),C77,$B$15,TRUE())-BINOMDIST(MIN(9,C77),C77,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C77),C77,$B$15,TRUE()))*$D$38)</f>
         <v>0</v>
       </c>
-      <c r="E77" s="26" t="n">
+      <c r="E77" s="43" t="n">
         <f aca="false">B77*D77</f>
         <v>0</v>
       </c>
@@ -8881,7 +8906,7 @@
       <c r="A78" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="B78" s="26" t="n">
+      <c r="B78" s="43" t="n">
         <f aca="false">BINOMDIST($A78,$B$7,$B$25,FALSE())</f>
         <v>3.08925093625218E-039</v>
       </c>
@@ -8889,11 +8914,11 @@
         <f aca="false">$B$7-$A78</f>
         <v>2</v>
       </c>
-      <c r="D78" s="28" t="n">
+      <c r="D78" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C78),C78,$B$15,TRUE())-BINOMDIST(MIN(7,C78),C78,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C78),C78,$B$15,TRUE())-BINOMDIST(MIN(9,C78),C78,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C78),C78,$B$15,TRUE()))*$D$38)</f>
         <v>0</v>
       </c>
-      <c r="E78" s="26" t="n">
+      <c r="E78" s="43" t="n">
         <f aca="false">B78*D78</f>
         <v>0</v>
       </c>
@@ -8902,7 +8927,7 @@
       <c r="A79" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="B79" s="26" t="n">
+      <c r="B79" s="43" t="n">
         <f aca="false">BINOMDIST($A79,$B$7,$B$25,FALSE())</f>
         <v>7.49871720086914E-042</v>
       </c>
@@ -8910,11 +8935,11 @@
         <f aca="false">$B$7-$A79</f>
         <v>1</v>
       </c>
-      <c r="D79" s="28" t="n">
+      <c r="D79" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C79),C79,$B$15,TRUE())-BINOMDIST(MIN(7,C79),C79,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C79),C79,$B$15,TRUE())-BINOMDIST(MIN(9,C79),C79,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C79),C79,$B$15,TRUE()))*$D$38)</f>
         <v>0</v>
       </c>
-      <c r="E79" s="26" t="n">
+      <c r="E79" s="43" t="n">
         <f aca="false">B79*D79</f>
         <v>0</v>
       </c>
@@ -8923,7 +8948,7 @@
       <c r="A80" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="B80" s="26" t="n">
+      <c r="B80" s="43" t="n">
         <f aca="false">BINOMDIST($A80,$B$7,$B$25,FALSE())</f>
         <v>8.79766683331784E-045</v>
       </c>
@@ -8931,11 +8956,11 @@
         <f aca="false">$B$7-$A80</f>
         <v>0</v>
       </c>
-      <c r="D80" s="28" t="n">
+      <c r="D80" s="44" t="n">
         <f aca="false">$C$34*((BINOMDIST(MIN(9,C80),C80,$B$15,TRUE())-BINOMDIST(MIN(7,C80),C80,$B$15,TRUE()))*$B$38+(BINOMDIST(MIN(11,C80),C80,$B$15,TRUE())-BINOMDIST(MIN(9,C80),C80,$B$15,TRUE()))*$C$38+(1-BINOMDIST(MIN(11,C80),C80,$B$15,TRUE()))*$D$38)</f>
         <v>0</v>
       </c>
-      <c r="E80" s="26" t="n">
+      <c r="E80" s="43" t="n">
         <f aca="false">B80*D80</f>
         <v>0</v>
       </c>
@@ -8944,13 +8969,13 @@
       <c r="A81" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="B81" s="26" t="n">
+      <c r="B81" s="43" t="n">
         <f aca="false">SUM(B50:B80)</f>
         <v>0.999999999999999</v>
       </c>
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
-      <c r="E81" s="25" t="n">
+      <c r="E81" s="42" t="n">
         <f aca="false">SUM(E50:E80)</f>
         <v>0.454427538088994</v>
       </c>
@@ -9074,7 +9099,7 @@
       <c r="B94" s="31" t="n">
         <v>1077</v>
       </c>
-      <c r="C94" s="23" t="n">
+      <c r="C94" s="41" t="n">
         <f aca="false">B94/10000</f>
         <v>0.1077</v>
       </c>
@@ -9089,7 +9114,7 @@
       <c r="B95" s="31" t="n">
         <v>1072</v>
       </c>
-      <c r="C95" s="23" t="n">
+      <c r="C95" s="41" t="n">
         <f aca="false">B95/10000</f>
         <v>0.1072</v>
       </c>
@@ -9104,7 +9129,7 @@
       <c r="B96" s="31" t="n">
         <v>1072</v>
       </c>
-      <c r="C96" s="23" t="n">
+      <c r="C96" s="41" t="n">
         <f aca="false">B96/10000</f>
         <v>0.1072</v>
       </c>
@@ -9119,7 +9144,7 @@
       <c r="B97" s="31" t="n">
         <v>1072</v>
       </c>
-      <c r="C97" s="23" t="n">
+      <c r="C97" s="41" t="n">
         <f aca="false">B97/10000</f>
         <v>0.1072</v>
       </c>
@@ -9134,7 +9159,7 @@
       <c r="B98" s="31" t="n">
         <v>1072</v>
       </c>
-      <c r="C98" s="23" t="n">
+      <c r="C98" s="41" t="n">
         <f aca="false">B98/10000</f>
         <v>0.1072</v>
       </c>
@@ -9149,7 +9174,7 @@
       <c r="B99" s="31" t="n">
         <v>1072</v>
       </c>
-      <c r="C99" s="23" t="n">
+      <c r="C99" s="41" t="n">
         <f aca="false">B99/10000</f>
         <v>0.1072</v>
       </c>
@@ -9164,7 +9189,7 @@
       <c r="B100" s="31" t="n">
         <v>1072</v>
       </c>
-      <c r="C100" s="23" t="n">
+      <c r="C100" s="41" t="n">
         <f aca="false">B100/10000</f>
         <v>0.1072</v>
       </c>
@@ -9179,7 +9204,7 @@
       <c r="B101" s="31" t="n">
         <v>1072</v>
       </c>
-      <c r="C101" s="23" t="n">
+      <c r="C101" s="41" t="n">
         <f aca="false">B101/10000</f>
         <v>0.1072</v>
       </c>
@@ -9194,7 +9219,7 @@
       <c r="B102" s="31" t="n">
         <v>1072</v>
       </c>
-      <c r="C102" s="23" t="n">
+      <c r="C102" s="41" t="n">
         <f aca="false">B102/10000</f>
         <v>0.1072</v>
       </c>
@@ -9209,7 +9234,7 @@
       <c r="B103" s="31" t="n">
         <v>300</v>
       </c>
-      <c r="C103" s="23" t="n">
+      <c r="C103" s="41" t="n">
         <f aca="false">B103/10000</f>
         <v>0.03</v>
       </c>
@@ -9224,7 +9249,7 @@
       <c r="B104" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="C104" s="23" t="n">
+      <c r="C104" s="41" t="n">
         <f aca="false">B104/10000</f>
         <v>0.0047</v>
       </c>
@@ -9240,7 +9265,7 @@
         <f aca="false">SUM(B94:B104)</f>
         <v>10000</v>
       </c>
-      <c r="C105" s="23" t="n">
+      <c r="C105" s="41" t="n">
         <f aca="false">B105/10000</f>
         <v>1</v>
       </c>
